--- a/data/2026-05-08/BallparkPal_Pitchers.xlsx
+++ b/data/2026-05-08/BallparkPal_Pitchers.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="104">
   <si>
     <t>GamePk</t>
   </si>
@@ -120,6 +120,213 @@
   </si>
   <si>
     <t>A</t>
+  </si>
+  <si>
+    <t>6:40</t>
+  </si>
+  <si>
+    <t>Jesus Luzardo</t>
+  </si>
+  <si>
+    <t>Luzardo</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>PHI</t>
+  </si>
+  <si>
+    <t>COL</t>
+  </si>
+  <si>
+    <t>Chase Dollander</t>
+  </si>
+  <si>
+    <t>Dollander</t>
+  </si>
+  <si>
+    <t>7:40</t>
+  </si>
+  <si>
+    <t>Max Fried</t>
+  </si>
+  <si>
+    <t>Fried</t>
+  </si>
+  <si>
+    <t>NYY</t>
+  </si>
+  <si>
+    <t>MIL</t>
+  </si>
+  <si>
+    <t>Jacob Misiorowski</t>
+  </si>
+  <si>
+    <t>Misiorowski</t>
+  </si>
+  <si>
+    <t>10:10</t>
+  </si>
+  <si>
+    <t>Chris Sale</t>
+  </si>
+  <si>
+    <t>Sale</t>
+  </si>
+  <si>
+    <t>ATL</t>
+  </si>
+  <si>
+    <t>LAD</t>
+  </si>
+  <si>
+    <t>Emmet Sheehan</t>
+  </si>
+  <si>
+    <t>Sheehan</t>
+  </si>
+  <si>
+    <t>Kris Bubic</t>
+  </si>
+  <si>
+    <t>Bubic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KC </t>
+  </si>
+  <si>
+    <t>DET</t>
+  </si>
+  <si>
+    <t>Keider Montero</t>
+  </si>
+  <si>
+    <t>Montero</t>
+  </si>
+  <si>
+    <t>7:15</t>
+  </si>
+  <si>
+    <t>Connor Prielipp</t>
+  </si>
+  <si>
+    <t>Prielipp</t>
+  </si>
+  <si>
+    <t>MIN</t>
+  </si>
+  <si>
+    <t>CLE</t>
+  </si>
+  <si>
+    <t>Parker Messick</t>
+  </si>
+  <si>
+    <t>Messick</t>
+  </si>
+  <si>
+    <t>6:10</t>
+  </si>
+  <si>
+    <t>Nick Lodolo</t>
+  </si>
+  <si>
+    <t>Lodolo</t>
+  </si>
+  <si>
+    <t>CIN</t>
+  </si>
+  <si>
+    <t>HOU</t>
+  </si>
+  <si>
+    <t>Mike Burrows</t>
+  </si>
+  <si>
+    <t>Burrows</t>
+  </si>
+  <si>
+    <t>Emerson Hancock</t>
+  </si>
+  <si>
+    <t>Hancock</t>
+  </si>
+  <si>
+    <t>SEA</t>
+  </si>
+  <si>
+    <t>CHW</t>
+  </si>
+  <si>
+    <t>Sean Burke</t>
+  </si>
+  <si>
+    <t>Burke</t>
+  </si>
+  <si>
+    <t>7:10</t>
+  </si>
+  <si>
+    <t>Jesse Scholtens</t>
+  </si>
+  <si>
+    <t>Scholtens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TB </t>
+  </si>
+  <si>
+    <t>BOS</t>
+  </si>
+  <si>
+    <t>Connelly Early</t>
+  </si>
+  <si>
+    <t>Early</t>
+  </si>
+  <si>
+    <t>7:05</t>
+  </si>
+  <si>
+    <t>Kyle Bradish</t>
+  </si>
+  <si>
+    <t>Bradish</t>
+  </si>
+  <si>
+    <t>BAL</t>
+  </si>
+  <si>
+    <t>ATH</t>
+  </si>
+  <si>
+    <t>Jacob Lopez</t>
+  </si>
+  <si>
+    <t>Lopez</t>
+  </si>
+  <si>
+    <t>9:40</t>
+  </si>
+  <si>
+    <t>Ryne Nelson</t>
+  </si>
+  <si>
+    <t>Nelson</t>
+  </si>
+  <si>
+    <t>ARI</t>
+  </si>
+  <si>
+    <t>NYM</t>
+  </si>
+  <si>
+    <t>Nolan McLean</t>
+  </si>
+  <si>
+    <t>McLean</t>
   </si>
 </sst>
 </file>
@@ -459,7 +666,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:X3"/>
+  <dimension ref="A1:X23"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:24">
@@ -568,46 +775,46 @@
         <v>31</v>
       </c>
       <c r="K2">
-        <v>21.937</v>
+        <v>22.216</v>
       </c>
       <c r="L2">
-        <v>5.209</v>
+        <v>5.299</v>
       </c>
       <c r="M2">
-        <v>0.349</v>
+        <v>0.341</v>
       </c>
       <c r="N2">
-        <v>0.225</v>
+        <v>0.221</v>
       </c>
       <c r="O2">
-        <v>0.426</v>
+        <v>0.438</v>
       </c>
       <c r="P2">
-        <v>0.329</v>
+        <v>0.352</v>
       </c>
       <c r="Q2">
-        <v>15.588</v>
+        <v>15.71</v>
       </c>
       <c r="R2">
-        <v>28.563</v>
+        <v>28.839</v>
       </c>
       <c r="S2">
-        <v>2.103</v>
+        <v>1.956</v>
       </c>
       <c r="T2">
-        <v>4.164</v>
+        <v>4.0</v>
       </c>
       <c r="U2">
-        <v>5.278</v>
+        <v>5.118</v>
       </c>
       <c r="V2">
-        <v>2.312</v>
+        <v>2.53</v>
       </c>
       <c r="W2">
-        <v>0.603</v>
+        <v>0.529</v>
       </c>
       <c r="X2">
-        <v>0.401</v>
+        <v>0.412</v>
       </c>
     </row>
     <row r="3" spans="1:24">
@@ -642,46 +849,1526 @@
         <v>30</v>
       </c>
       <c r="K3">
-        <v>21.879</v>
+        <v>22.225</v>
       </c>
       <c r="L3">
-        <v>4.999</v>
+        <v>5.151</v>
       </c>
       <c r="M3">
+        <v>0.151</v>
+      </c>
+      <c r="N3">
+        <v>0.42</v>
+      </c>
+      <c r="O3">
+        <v>0.429</v>
+      </c>
+      <c r="P3">
+        <v>0.3</v>
+      </c>
+      <c r="Q3">
+        <v>9.256</v>
+      </c>
+      <c r="R3">
+        <v>19.477</v>
+      </c>
+      <c r="S3">
+        <v>2.729</v>
+      </c>
+      <c r="T3">
+        <v>5.289</v>
+      </c>
+      <c r="U3">
+        <v>3.369</v>
+      </c>
+      <c r="V3">
+        <v>1.747</v>
+      </c>
+      <c r="W3">
+        <v>0.838</v>
+      </c>
+      <c r="X3">
+        <v>0.388</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24">
+      <c r="A4">
+        <v>823466</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4">
+        <v>666200</v>
+      </c>
+      <c r="E4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J4" t="s">
+        <v>40</v>
+      </c>
+      <c r="K4">
+        <v>24.484</v>
+      </c>
+      <c r="L4">
+        <v>6.038</v>
+      </c>
+      <c r="M4">
+        <v>0.417</v>
+      </c>
+      <c r="N4">
+        <v>0.217</v>
+      </c>
+      <c r="O4">
+        <v>0.366</v>
+      </c>
+      <c r="P4">
+        <v>0.57</v>
+      </c>
+      <c r="Q4">
+        <v>23.408</v>
+      </c>
+      <c r="R4">
+        <v>40.894</v>
+      </c>
+      <c r="S4">
+        <v>1.962</v>
+      </c>
+      <c r="T4">
+        <v>5.162</v>
+      </c>
+      <c r="U4">
+        <v>7.962</v>
+      </c>
+      <c r="V4">
+        <v>1.334</v>
+      </c>
+      <c r="W4">
+        <v>0.525</v>
+      </c>
+      <c r="X4">
+        <v>0.508</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24">
+      <c r="A5">
+        <v>823466</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5">
+        <v>801403</v>
+      </c>
+      <c r="E5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" t="s">
+        <v>34</v>
+      </c>
+      <c r="I5" t="s">
+        <v>40</v>
+      </c>
+      <c r="J5" t="s">
+        <v>39</v>
+      </c>
+      <c r="K5">
+        <v>22.164</v>
+      </c>
+      <c r="L5">
+        <v>5.147</v>
+      </c>
+      <c r="M5">
+        <v>0.139</v>
+      </c>
+      <c r="N5">
+        <v>0.422</v>
+      </c>
+      <c r="O5">
+        <v>0.439</v>
+      </c>
+      <c r="P5">
+        <v>0.318</v>
+      </c>
+      <c r="Q5">
+        <v>12.892</v>
+      </c>
+      <c r="R5">
+        <v>24.989</v>
+      </c>
+      <c r="S5">
+        <v>2.389</v>
+      </c>
+      <c r="T5">
+        <v>4.646</v>
+      </c>
+      <c r="U5">
+        <v>4.869</v>
+      </c>
+      <c r="V5">
+        <v>2.387</v>
+      </c>
+      <c r="W5">
+        <v>0.632</v>
+      </c>
+      <c r="X5">
+        <v>0.833</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24">
+      <c r="A6">
+        <v>823794</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6">
+        <v>608331</v>
+      </c>
+      <c r="E6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I6" t="s">
+        <v>46</v>
+      </c>
+      <c r="J6" t="s">
+        <v>47</v>
+      </c>
+      <c r="K6">
+        <v>23.595</v>
+      </c>
+      <c r="L6">
+        <v>5.741</v>
+      </c>
+      <c r="M6">
+        <v>0.238</v>
+      </c>
+      <c r="N6">
+        <v>0.294</v>
+      </c>
+      <c r="O6">
+        <v>0.468</v>
+      </c>
+      <c r="P6">
+        <v>0.523</v>
+      </c>
+      <c r="Q6">
+        <v>15.234</v>
+      </c>
+      <c r="R6">
+        <v>28.843</v>
+      </c>
+      <c r="S6">
+        <v>2.064</v>
+      </c>
+      <c r="T6">
+        <v>4.487</v>
+      </c>
+      <c r="U6">
+        <v>4.763</v>
+      </c>
+      <c r="V6">
+        <v>2.272</v>
+      </c>
+      <c r="W6">
+        <v>0.478</v>
+      </c>
+      <c r="X6">
+        <v>0.568</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24">
+      <c r="A7">
+        <v>823794</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7">
+        <v>694819</v>
+      </c>
+      <c r="E7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F7" t="s">
+        <v>49</v>
+      </c>
+      <c r="G7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" t="s">
+        <v>29</v>
+      </c>
+      <c r="I7" t="s">
+        <v>47</v>
+      </c>
+      <c r="J7" t="s">
+        <v>46</v>
+      </c>
+      <c r="K7">
+        <v>22.073</v>
+      </c>
+      <c r="L7">
+        <v>5.303</v>
+      </c>
+      <c r="M7">
+        <v>0.251</v>
+      </c>
+      <c r="N7">
+        <v>0.313</v>
+      </c>
+      <c r="O7">
+        <v>0.436</v>
+      </c>
+      <c r="P7">
+        <v>0.356</v>
+      </c>
+      <c r="Q7">
+        <v>23.426</v>
+      </c>
+      <c r="R7">
+        <v>40.166</v>
+      </c>
+      <c r="S7">
+        <v>1.798</v>
+      </c>
+      <c r="T7">
+        <v>3.251</v>
+      </c>
+      <c r="U7">
+        <v>8.907</v>
+      </c>
+      <c r="V7">
+        <v>2.972</v>
+      </c>
+      <c r="W7">
+        <v>0.701</v>
+      </c>
+      <c r="X7">
+        <v>0.468</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24">
+      <c r="A8">
+        <v>823957</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8">
+        <v>519242</v>
+      </c>
+      <c r="E8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H8" t="s">
+        <v>34</v>
+      </c>
+      <c r="I8" t="s">
+        <v>53</v>
+      </c>
+      <c r="J8" t="s">
+        <v>54</v>
+      </c>
+      <c r="K8">
+        <v>23.184</v>
+      </c>
+      <c r="L8">
+        <v>5.503</v>
+      </c>
+      <c r="M8">
+        <v>0.202</v>
+      </c>
+      <c r="N8">
+        <v>0.349</v>
+      </c>
+      <c r="O8">
+        <v>0.448</v>
+      </c>
+      <c r="P8">
+        <v>0.405</v>
+      </c>
+      <c r="Q8">
+        <v>15.456</v>
+      </c>
+      <c r="R8">
+        <v>28.888</v>
+      </c>
+      <c r="S8">
+        <v>2.556</v>
+      </c>
+      <c r="T8">
+        <v>4.727</v>
+      </c>
+      <c r="U8">
+        <v>5.738</v>
+      </c>
+      <c r="V8">
+        <v>2.124</v>
+      </c>
+      <c r="W8">
+        <v>0.907</v>
+      </c>
+      <c r="X8">
+        <v>0.363</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24">
+      <c r="A9">
+        <v>823957</v>
+      </c>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9">
+        <v>686218</v>
+      </c>
+      <c r="E9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9" t="s">
+        <v>56</v>
+      </c>
+      <c r="G9" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I9" t="s">
+        <v>54</v>
+      </c>
+      <c r="J9" t="s">
+        <v>53</v>
+      </c>
+      <c r="K9">
+        <v>19.699</v>
+      </c>
+      <c r="L9">
+        <v>4.722</v>
+      </c>
+      <c r="M9">
+        <v>0.211</v>
+      </c>
+      <c r="N9">
+        <v>0.26</v>
+      </c>
+      <c r="O9">
+        <v>0.529</v>
+      </c>
+      <c r="P9">
+        <v>0.152</v>
+      </c>
+      <c r="Q9">
+        <v>14.812</v>
+      </c>
+      <c r="R9">
+        <v>26.077</v>
+      </c>
+      <c r="S9">
+        <v>1.952</v>
+      </c>
+      <c r="T9">
+        <v>4.12</v>
+      </c>
+      <c r="U9">
+        <v>5.297</v>
+      </c>
+      <c r="V9">
+        <v>1.462</v>
+      </c>
+      <c r="W9">
+        <v>0.644</v>
+      </c>
+      <c r="X9">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24">
+      <c r="A10">
+        <v>824116</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10">
+        <v>663460</v>
+      </c>
+      <c r="E10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F10" t="s">
+        <v>58</v>
+      </c>
+      <c r="G10" t="s">
+        <v>38</v>
+      </c>
+      <c r="H10" t="s">
+        <v>29</v>
+      </c>
+      <c r="I10" t="s">
+        <v>59</v>
+      </c>
+      <c r="J10" t="s">
+        <v>60</v>
+      </c>
+      <c r="K10">
+        <v>23.074</v>
+      </c>
+      <c r="L10">
+        <v>5.528</v>
+      </c>
+      <c r="M10">
+        <v>0.298</v>
+      </c>
+      <c r="N10">
+        <v>0.292</v>
+      </c>
+      <c r="O10">
+        <v>0.41</v>
+      </c>
+      <c r="P10">
+        <v>0.409</v>
+      </c>
+      <c r="Q10">
+        <v>14.973</v>
+      </c>
+      <c r="R10">
+        <v>27.974</v>
+      </c>
+      <c r="S10">
+        <v>2.161</v>
+      </c>
+      <c r="T10">
+        <v>4.28</v>
+      </c>
+      <c r="U10">
+        <v>4.817</v>
+      </c>
+      <c r="V10">
+        <v>2.376</v>
+      </c>
+      <c r="W10">
+        <v>0.606</v>
+      </c>
+      <c r="X10">
+        <v>0.279</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24">
+      <c r="A11">
+        <v>824116</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11">
+        <v>672456</v>
+      </c>
+      <c r="E11" t="s">
+        <v>61</v>
+      </c>
+      <c r="F11" t="s">
+        <v>62</v>
+      </c>
+      <c r="G11" t="s">
+        <v>28</v>
+      </c>
+      <c r="H11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I11" t="s">
+        <v>60</v>
+      </c>
+      <c r="J11" t="s">
+        <v>59</v>
+      </c>
+      <c r="K11">
+        <v>21.852</v>
+      </c>
+      <c r="L11">
+        <v>5.252</v>
+      </c>
+      <c r="M11">
+        <v>0.187</v>
+      </c>
+      <c r="N11">
+        <v>0.325</v>
+      </c>
+      <c r="O11">
+        <v>0.488</v>
+      </c>
+      <c r="P11">
+        <v>0.327</v>
+      </c>
+      <c r="Q11">
+        <v>10.716</v>
+      </c>
+      <c r="R11">
+        <v>20.993</v>
+      </c>
+      <c r="S11">
+        <v>2.28</v>
+      </c>
+      <c r="T11">
+        <v>4.646</v>
+      </c>
+      <c r="U11">
+        <v>3.216</v>
+      </c>
+      <c r="V11">
+        <v>1.572</v>
+      </c>
+      <c r="W11">
+        <v>0.624</v>
+      </c>
+      <c r="X11">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24">
+      <c r="A12">
+        <v>824443</v>
+      </c>
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" t="s">
+        <v>63</v>
+      </c>
+      <c r="D12">
+        <v>687570</v>
+      </c>
+      <c r="E12" t="s">
+        <v>64</v>
+      </c>
+      <c r="F12" t="s">
+        <v>65</v>
+      </c>
+      <c r="G12" t="s">
+        <v>38</v>
+      </c>
+      <c r="H12" t="s">
+        <v>34</v>
+      </c>
+      <c r="I12" t="s">
+        <v>66</v>
+      </c>
+      <c r="J12" t="s">
+        <v>67</v>
+      </c>
+      <c r="K12">
+        <v>21.116</v>
+      </c>
+      <c r="L12">
+        <v>4.975</v>
+      </c>
+      <c r="M12">
+        <v>0.165</v>
+      </c>
+      <c r="N12">
+        <v>0.351</v>
+      </c>
+      <c r="O12">
+        <v>0.483</v>
+      </c>
+      <c r="P12">
+        <v>0.247</v>
+      </c>
+      <c r="Q12">
+        <v>13.597</v>
+      </c>
+      <c r="R12">
+        <v>25.231</v>
+      </c>
+      <c r="S12">
+        <v>1.956</v>
+      </c>
+      <c r="T12">
+        <v>3.811</v>
+      </c>
+      <c r="U12">
+        <v>4.732</v>
+      </c>
+      <c r="V12">
+        <v>2.546</v>
+      </c>
+      <c r="W12">
+        <v>0.49</v>
+      </c>
+      <c r="X12">
+        <v>0.488</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24">
+      <c r="A13">
+        <v>824443</v>
+      </c>
+      <c r="B13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" t="s">
+        <v>63</v>
+      </c>
+      <c r="D13">
+        <v>800048</v>
+      </c>
+      <c r="E13" t="s">
+        <v>68</v>
+      </c>
+      <c r="F13" t="s">
+        <v>69</v>
+      </c>
+      <c r="G13" t="s">
+        <v>38</v>
+      </c>
+      <c r="H13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I13" t="s">
+        <v>67</v>
+      </c>
+      <c r="J13" t="s">
+        <v>66</v>
+      </c>
+      <c r="K13">
+        <v>23.904</v>
+      </c>
+      <c r="L13">
+        <v>5.975</v>
+      </c>
+      <c r="M13">
+        <v>0.36</v>
+      </c>
+      <c r="N13">
+        <v>0.26</v>
+      </c>
+      <c r="O13">
+        <v>0.38</v>
+      </c>
+      <c r="P13">
+        <v>0.551</v>
+      </c>
+      <c r="Q13">
+        <v>19.469</v>
+      </c>
+      <c r="R13">
+        <v>34.605</v>
+      </c>
+      <c r="S13">
+        <v>1.88</v>
+      </c>
+      <c r="T13">
+        <v>4.492</v>
+      </c>
+      <c r="U13">
+        <v>5.984</v>
+      </c>
+      <c r="V13">
+        <v>1.643</v>
+      </c>
+      <c r="W13">
+        <v>0.6</v>
+      </c>
+      <c r="X13">
+        <v>0.392</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24">
+      <c r="A14">
+        <v>824522</v>
+      </c>
+      <c r="B14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D14">
+        <v>666157</v>
+      </c>
+      <c r="E14" t="s">
+        <v>71</v>
+      </c>
+      <c r="F14" t="s">
+        <v>72</v>
+      </c>
+      <c r="G14" t="s">
+        <v>38</v>
+      </c>
+      <c r="H14" t="s">
+        <v>29</v>
+      </c>
+      <c r="I14" t="s">
+        <v>73</v>
+      </c>
+      <c r="J14" t="s">
+        <v>74</v>
+      </c>
+      <c r="K14">
+        <v>21.001</v>
+      </c>
+      <c r="L14">
+        <v>5.307</v>
+      </c>
+      <c r="M14">
+        <v>0.338</v>
+      </c>
+      <c r="N14">
+        <v>0.186</v>
+      </c>
+      <c r="O14">
+        <v>0.476</v>
+      </c>
+      <c r="P14">
+        <v>0.349</v>
+      </c>
+      <c r="Q14">
+        <v>19.073</v>
+      </c>
+      <c r="R14">
+        <v>32.616</v>
+      </c>
+      <c r="S14">
+        <v>1.591</v>
+      </c>
+      <c r="T14">
+        <v>3.934</v>
+      </c>
+      <c r="U14">
+        <v>6.016</v>
+      </c>
+      <c r="V14">
+        <v>1.206</v>
+      </c>
+      <c r="W14">
+        <v>0.594</v>
+      </c>
+      <c r="X14">
+        <v>0.295</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24">
+      <c r="A15">
+        <v>824522</v>
+      </c>
+      <c r="B15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" t="s">
+        <v>70</v>
+      </c>
+      <c r="D15">
+        <v>681347</v>
+      </c>
+      <c r="E15" t="s">
+        <v>75</v>
+      </c>
+      <c r="F15" t="s">
+        <v>76</v>
+      </c>
+      <c r="G15" t="s">
+        <v>28</v>
+      </c>
+      <c r="H15" t="s">
+        <v>34</v>
+      </c>
+      <c r="I15" t="s">
+        <v>74</v>
+      </c>
+      <c r="J15" t="s">
+        <v>73</v>
+      </c>
+      <c r="K15">
+        <v>21.557</v>
+      </c>
+      <c r="L15">
+        <v>4.958</v>
+      </c>
+      <c r="M15">
+        <v>0.129</v>
+      </c>
+      <c r="N15">
+        <v>0.401</v>
+      </c>
+      <c r="O15">
+        <v>0.469</v>
+      </c>
+      <c r="P15">
+        <v>0.251</v>
+      </c>
+      <c r="Q15">
+        <v>11.037</v>
+      </c>
+      <c r="R15">
+        <v>21.853</v>
+      </c>
+      <c r="S15">
+        <v>2.531</v>
+      </c>
+      <c r="T15">
+        <v>4.68</v>
+      </c>
+      <c r="U15">
+        <v>4.264</v>
+      </c>
+      <c r="V15">
+        <v>2.165</v>
+      </c>
+      <c r="W15">
+        <v>0.802</v>
+      </c>
+      <c r="X15">
+        <v>0.623</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24">
+      <c r="A16">
+        <v>824607</v>
+      </c>
+      <c r="B16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16">
+        <v>676106</v>
+      </c>
+      <c r="E16" t="s">
+        <v>77</v>
+      </c>
+      <c r="F16" t="s">
+        <v>78</v>
+      </c>
+      <c r="G16" t="s">
+        <v>28</v>
+      </c>
+      <c r="H16" t="s">
+        <v>34</v>
+      </c>
+      <c r="I16" t="s">
+        <v>79</v>
+      </c>
+      <c r="J16" t="s">
+        <v>80</v>
+      </c>
+      <c r="K16">
+        <v>18.992</v>
+      </c>
+      <c r="L16">
+        <v>4.684</v>
+      </c>
+      <c r="M16">
+        <v>0.148</v>
+      </c>
+      <c r="N16">
+        <v>0.254</v>
+      </c>
+      <c r="O16">
+        <v>0.598</v>
+      </c>
+      <c r="P16">
         <v>0.138</v>
       </c>
-      <c r="N3">
-        <v>0.436</v>
-      </c>
-      <c r="O3">
-        <v>0.426</v>
-      </c>
-      <c r="P3">
-        <v>0.251</v>
-      </c>
-      <c r="Q3">
-        <v>8.32</v>
-      </c>
-      <c r="R3">
-        <v>18.018</v>
-      </c>
-      <c r="S3">
-        <v>2.835</v>
-      </c>
-      <c r="T3">
-        <v>5.301</v>
-      </c>
-      <c r="U3">
-        <v>3.233</v>
-      </c>
-      <c r="V3">
-        <v>1.824</v>
-      </c>
-      <c r="W3">
-        <v>0.87</v>
-      </c>
-      <c r="X3">
-        <v>0.327</v>
+      <c r="Q16">
+        <v>15.125</v>
+      </c>
+      <c r="R16">
+        <v>25.991</v>
+      </c>
+      <c r="S16">
+        <v>1.607</v>
+      </c>
+      <c r="T16">
+        <v>3.612</v>
+      </c>
+      <c r="U16">
+        <v>5.107</v>
+      </c>
+      <c r="V16">
+        <v>1.411</v>
+      </c>
+      <c r="W16">
+        <v>0.539</v>
+      </c>
+      <c r="X16">
+        <v>0.268</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24">
+      <c r="A17">
+        <v>824607</v>
+      </c>
+      <c r="B17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17">
+        <v>680732</v>
+      </c>
+      <c r="E17" t="s">
+        <v>81</v>
+      </c>
+      <c r="F17" t="s">
+        <v>82</v>
+      </c>
+      <c r="G17" t="s">
+        <v>28</v>
+      </c>
+      <c r="H17" t="s">
+        <v>29</v>
+      </c>
+      <c r="I17" t="s">
+        <v>80</v>
+      </c>
+      <c r="J17" t="s">
+        <v>79</v>
+      </c>
+      <c r="K17">
+        <v>23.192</v>
+      </c>
+      <c r="L17">
+        <v>5.647</v>
+      </c>
+      <c r="M17">
+        <v>0.259</v>
+      </c>
+      <c r="N17">
+        <v>0.355</v>
+      </c>
+      <c r="O17">
+        <v>0.387</v>
+      </c>
+      <c r="P17">
+        <v>0.441</v>
+      </c>
+      <c r="Q17">
+        <v>17.838</v>
+      </c>
+      <c r="R17">
+        <v>32.059</v>
+      </c>
+      <c r="S17">
+        <v>2.095</v>
+      </c>
+      <c r="T17">
+        <v>4.588</v>
+      </c>
+      <c r="U17">
+        <v>6.028</v>
+      </c>
+      <c r="V17">
+        <v>1.738</v>
+      </c>
+      <c r="W17">
+        <v>0.686</v>
+      </c>
+      <c r="X17">
+        <v>0.558</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24">
+      <c r="A18">
+        <v>824768</v>
+      </c>
+      <c r="B18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" t="s">
+        <v>83</v>
+      </c>
+      <c r="D18">
+        <v>669947</v>
+      </c>
+      <c r="E18" t="s">
+        <v>84</v>
+      </c>
+      <c r="F18" t="s">
+        <v>85</v>
+      </c>
+      <c r="G18" t="s">
+        <v>28</v>
+      </c>
+      <c r="H18" t="s">
+        <v>34</v>
+      </c>
+      <c r="I18" t="s">
+        <v>86</v>
+      </c>
+      <c r="J18" t="s">
+        <v>87</v>
+      </c>
+      <c r="K18">
+        <v>21.667</v>
+      </c>
+      <c r="L18">
+        <v>4.751</v>
+      </c>
+      <c r="M18">
+        <v>0.134</v>
+      </c>
+      <c r="N18">
+        <v>0.394</v>
+      </c>
+      <c r="O18">
+        <v>0.472</v>
+      </c>
+      <c r="P18">
+        <v>0.193</v>
+      </c>
+      <c r="Q18">
+        <v>8.744</v>
+      </c>
+      <c r="R18">
+        <v>19.052</v>
+      </c>
+      <c r="S18">
+        <v>2.916</v>
+      </c>
+      <c r="T18">
+        <v>5.722</v>
+      </c>
+      <c r="U18">
+        <v>3.991</v>
+      </c>
+      <c r="V18">
+        <v>2.003</v>
+      </c>
+      <c r="W18">
+        <v>0.619</v>
+      </c>
+      <c r="X18">
+        <v>0.558</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24">
+      <c r="A19">
+        <v>824768</v>
+      </c>
+      <c r="B19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" t="s">
+        <v>83</v>
+      </c>
+      <c r="D19">
+        <v>813349</v>
+      </c>
+      <c r="E19" t="s">
+        <v>88</v>
+      </c>
+      <c r="F19" t="s">
+        <v>89</v>
+      </c>
+      <c r="G19" t="s">
+        <v>38</v>
+      </c>
+      <c r="H19" t="s">
+        <v>29</v>
+      </c>
+      <c r="I19" t="s">
+        <v>87</v>
+      </c>
+      <c r="J19" t="s">
+        <v>86</v>
+      </c>
+      <c r="K19">
+        <v>22.566</v>
+      </c>
+      <c r="L19">
+        <v>5.297</v>
+      </c>
+      <c r="M19">
+        <v>0.334</v>
+      </c>
+      <c r="N19">
+        <v>0.235</v>
+      </c>
+      <c r="O19">
+        <v>0.43</v>
+      </c>
+      <c r="P19">
+        <v>0.337</v>
+      </c>
+      <c r="Q19">
+        <v>12.192</v>
+      </c>
+      <c r="R19">
+        <v>23.965</v>
+      </c>
+      <c r="S19">
+        <v>2.294</v>
+      </c>
+      <c r="T19">
+        <v>5.169</v>
+      </c>
+      <c r="U19">
+        <v>3.867</v>
+      </c>
+      <c r="V19">
+        <v>1.866</v>
+      </c>
+      <c r="W19">
+        <v>0.472</v>
+      </c>
+      <c r="X19">
+        <v>0.389</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24">
+      <c r="A20">
+        <v>824846</v>
+      </c>
+      <c r="B20" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" t="s">
+        <v>90</v>
+      </c>
+      <c r="D20">
+        <v>680694</v>
+      </c>
+      <c r="E20" t="s">
+        <v>91</v>
+      </c>
+      <c r="F20" t="s">
+        <v>92</v>
+      </c>
+      <c r="G20" t="s">
+        <v>28</v>
+      </c>
+      <c r="H20" t="s">
+        <v>29</v>
+      </c>
+      <c r="I20" t="s">
+        <v>93</v>
+      </c>
+      <c r="J20" t="s">
+        <v>94</v>
+      </c>
+      <c r="K20">
+        <v>22.666</v>
+      </c>
+      <c r="L20">
+        <v>5.17</v>
+      </c>
+      <c r="M20">
+        <v>0.299</v>
+      </c>
+      <c r="N20">
+        <v>0.272</v>
+      </c>
+      <c r="O20">
+        <v>0.429</v>
+      </c>
+      <c r="P20">
+        <v>0.3</v>
+      </c>
+      <c r="Q20">
+        <v>13.854</v>
+      </c>
+      <c r="R20">
+        <v>26.728</v>
+      </c>
+      <c r="S20">
+        <v>2.373</v>
+      </c>
+      <c r="T20">
+        <v>5.072</v>
+      </c>
+      <c r="U20">
+        <v>5.114</v>
+      </c>
+      <c r="V20">
+        <v>2.361</v>
+      </c>
+      <c r="W20">
+        <v>0.553</v>
+      </c>
+      <c r="X20">
+        <v>0.205</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24">
+      <c r="A21">
+        <v>824846</v>
+      </c>
+      <c r="B21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" t="s">
+        <v>90</v>
+      </c>
+      <c r="D21">
+        <v>682052</v>
+      </c>
+      <c r="E21" t="s">
+        <v>95</v>
+      </c>
+      <c r="F21" t="s">
+        <v>96</v>
+      </c>
+      <c r="G21" t="s">
+        <v>38</v>
+      </c>
+      <c r="H21" t="s">
+        <v>34</v>
+      </c>
+      <c r="I21" t="s">
+        <v>94</v>
+      </c>
+      <c r="J21" t="s">
+        <v>93</v>
+      </c>
+      <c r="K21">
+        <v>21.419</v>
+      </c>
+      <c r="L21">
+        <v>4.75</v>
+      </c>
+      <c r="M21">
+        <v>0.154</v>
+      </c>
+      <c r="N21">
+        <v>0.352</v>
+      </c>
+      <c r="O21">
+        <v>0.494</v>
+      </c>
+      <c r="P21">
+        <v>0.213</v>
+      </c>
+      <c r="Q21">
+        <v>9.35</v>
+      </c>
+      <c r="R21">
+        <v>19.674</v>
+      </c>
+      <c r="S21">
+        <v>2.659</v>
+      </c>
+      <c r="T21">
+        <v>4.456</v>
+      </c>
+      <c r="U21">
+        <v>3.876</v>
+      </c>
+      <c r="V21">
+        <v>2.857</v>
+      </c>
+      <c r="W21">
+        <v>0.659</v>
+      </c>
+      <c r="X21">
+        <v>0.429</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24">
+      <c r="A22">
+        <v>825088</v>
+      </c>
+      <c r="B22" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" t="s">
+        <v>97</v>
+      </c>
+      <c r="D22">
+        <v>669194</v>
+      </c>
+      <c r="E22" t="s">
+        <v>98</v>
+      </c>
+      <c r="F22" t="s">
+        <v>99</v>
+      </c>
+      <c r="G22" t="s">
+        <v>28</v>
+      </c>
+      <c r="H22" t="s">
+        <v>29</v>
+      </c>
+      <c r="I22" t="s">
+        <v>100</v>
+      </c>
+      <c r="J22" t="s">
+        <v>101</v>
+      </c>
+      <c r="K22">
+        <v>22.812</v>
+      </c>
+      <c r="L22">
+        <v>5.283</v>
+      </c>
+      <c r="M22">
+        <v>0.215</v>
+      </c>
+      <c r="N22">
+        <v>0.38</v>
+      </c>
+      <c r="O22">
+        <v>0.405</v>
+      </c>
+      <c r="P22">
+        <v>0.329</v>
+      </c>
+      <c r="Q22">
+        <v>12.109</v>
+      </c>
+      <c r="R22">
+        <v>23.868</v>
+      </c>
+      <c r="S22">
+        <v>2.641</v>
+      </c>
+      <c r="T22">
+        <v>5.313</v>
+      </c>
+      <c r="U22">
+        <v>4.445</v>
+      </c>
+      <c r="V22">
+        <v>1.776</v>
+      </c>
+      <c r="W22">
+        <v>0.722</v>
+      </c>
+      <c r="X22">
+        <v>0.253</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24">
+      <c r="A23">
+        <v>825088</v>
+      </c>
+      <c r="B23" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" t="s">
+        <v>97</v>
+      </c>
+      <c r="D23">
+        <v>690997</v>
+      </c>
+      <c r="E23" t="s">
+        <v>102</v>
+      </c>
+      <c r="F23" t="s">
+        <v>103</v>
+      </c>
+      <c r="G23" t="s">
+        <v>28</v>
+      </c>
+      <c r="H23" t="s">
+        <v>34</v>
+      </c>
+      <c r="I23" t="s">
+        <v>101</v>
+      </c>
+      <c r="J23" t="s">
+        <v>100</v>
+      </c>
+      <c r="K23">
+        <v>22.838</v>
+      </c>
+      <c r="L23">
+        <v>5.417</v>
+      </c>
+      <c r="M23">
+        <v>0.247</v>
+      </c>
+      <c r="N23">
+        <v>0.237</v>
+      </c>
+      <c r="O23">
+        <v>0.516</v>
+      </c>
+      <c r="P23">
+        <v>0.392</v>
+      </c>
+      <c r="Q23">
+        <v>16.682</v>
+      </c>
+      <c r="R23">
+        <v>30.63</v>
+      </c>
+      <c r="S23">
+        <v>2.177</v>
+      </c>
+      <c r="T23">
+        <v>4.772</v>
+      </c>
+      <c r="U23">
+        <v>5.955</v>
+      </c>
+      <c r="V23">
+        <v>1.986</v>
+      </c>
+      <c r="W23">
+        <v>0.491</v>
+      </c>
+      <c r="X23">
+        <v>0.296</v>
       </c>
     </row>
   </sheetData>
